--- a/vdata.xlsx
+++ b/vdata.xlsx
@@ -9,10 +9,10 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18780" windowHeight="7080" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18780" windowHeight="7080"/>
   </bookViews>
   <sheets>
-    <sheet name="INFO" sheetId="4" r:id="rId1"/>
+    <sheet name="INFO" sheetId="9" r:id="rId1"/>
     <sheet name="CRIT" sheetId="5" r:id="rId2"/>
     <sheet name="PREC" sheetId="8" r:id="rId3"/>
     <sheet name="DATA" sheetId="1" r:id="rId4"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="74">
   <si>
     <t>Projekt</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Unternehmen</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>Methode</t>
   </si>
   <si>
@@ -98,12 +95,6 @@
     <t>Analyt</t>
   </si>
   <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
     <t>max VK intra</t>
   </si>
   <si>
@@ -167,43 +158,97 @@
     <t>Klinische Chemie</t>
   </si>
   <si>
-    <t>ng/ml</t>
-  </si>
-  <si>
-    <t>EDTA Hämolysat</t>
-  </si>
-  <si>
-    <t>ECLIA</t>
-  </si>
-  <si>
-    <t>DxI</t>
-  </si>
-  <si>
-    <t>Beckman</t>
-  </si>
-  <si>
-    <t>Maya v Arx</t>
-  </si>
-  <si>
-    <t>Oliver Speer</t>
-  </si>
-  <si>
-    <t>Anina Kühn</t>
-  </si>
-  <si>
-    <t>140-836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Folsre </t>
-  </si>
-  <si>
-    <t>Folsre</t>
-  </si>
-  <si>
-    <t>DxI 2 gefr</t>
-  </si>
-  <si>
-    <t>DxI 1 gefr</t>
+    <t>ZLM</t>
+  </si>
+  <si>
+    <t>07.08.23/AU1</t>
+  </si>
+  <si>
+    <t>08.08.23/AU1</t>
+  </si>
+  <si>
+    <t>09.08.23/AU1</t>
+  </si>
+  <si>
+    <t>10.08.23/AU1</t>
+  </si>
+  <si>
+    <t>11.08.23/AU1</t>
+  </si>
+  <si>
+    <t>12.08.23/AU1</t>
+  </si>
+  <si>
+    <t>13.08.23/AU1</t>
+  </si>
+  <si>
+    <t>10.09.23/AU1</t>
+  </si>
+  <si>
+    <t>12.09.23/AU1</t>
+  </si>
+  <si>
+    <t>13.09.23/AU1</t>
+  </si>
+  <si>
+    <t>07.08.23/AU2</t>
+  </si>
+  <si>
+    <t>08.08.23/AU2</t>
+  </si>
+  <si>
+    <t>09.08.23/AU2</t>
+  </si>
+  <si>
+    <t>10.08.23/AU2</t>
+  </si>
+  <si>
+    <t>11.08.23/AU2</t>
+  </si>
+  <si>
+    <t>12.08.23/AU2</t>
+  </si>
+  <si>
+    <t>13.08.23/AU2</t>
+  </si>
+  <si>
+    <t>10.09.23/AU2</t>
+  </si>
+  <si>
+    <t>12.09.23/AU2</t>
+  </si>
+  <si>
+    <t>13.09.23/AU2</t>
+  </si>
+  <si>
+    <t>g/L</t>
+  </si>
+  <si>
+    <t>BNII</t>
+  </si>
+  <si>
+    <t>AU5800</t>
+  </si>
+  <si>
+    <t>Heparin</t>
+  </si>
+  <si>
+    <t>Immuno-Turbidimetrie</t>
+  </si>
+  <si>
+    <t>Serum</t>
+  </si>
+  <si>
+    <t>Julien</t>
+  </si>
+  <si>
+    <t>Feb/Mrz 2024</t>
+  </si>
+  <si>
+    <t>ApoB Nephelometrie</t>
+  </si>
+  <si>
+    <t>Lp(a)</t>
   </si>
 </sst>
 </file>
@@ -214,7 +259,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,14 +301,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -297,7 +334,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -398,16 +435,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -461,24 +507,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -500,29 +528,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -549,51 +555,95 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -603,7 +653,7 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
+  <dxfs count="26">
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <fill>
@@ -613,6 +663,16 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
@@ -673,7 +733,7 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
@@ -870,63 +930,6 @@
     <dxf>
       <protection locked="0" hidden="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -941,17 +944,6 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:C22" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
-  <tableColumns count="3">
-    <tableColumn id="1" name="Methode" dataDxfId="28"/>
-    <tableColumn id="2" name="x" dataDxfId="27"/>
-    <tableColumn id="3" name="y" dataDxfId="26"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabelle2" displayName="Tabelle2" ref="A1:I2" totalsRowShown="0" dataDxfId="25">
   <autoFilter ref="A1:I2"/>
   <tableColumns count="9">
@@ -969,7 +961,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabelle3" displayName="Tabelle3" ref="A1:L11" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
   <autoFilter ref="A1:L11"/>
   <tableColumns count="12">
@@ -1253,286 +1245,199 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" customWidth="1"/>
-    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.85546875" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="57" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="51" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="58" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="32"/>
-      <c r="L1" s="1"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-    </row>
-    <row r="2" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="32"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="32"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="32"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="32"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="32"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="32"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="B7" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="42" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="32"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="32"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="32"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="32"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="32"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+      <c r="B8" s="60"/>
+      <c r="C8" s="57"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="61"/>
+      <c r="C9" s="62"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="63"/>
+      <c r="C10" s="64"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="65"/>
+      <c r="C11" s="62"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="32"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="32"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
+      <c r="B14" s="56"/>
+      <c r="C14" s="57"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="58"/>
+      <c r="C15" s="59"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="69" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="69" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="32"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="32"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="32"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="32"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
+      <c r="B17" s="66"/>
+      <c r="C17" s="59"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="45"/>
-      <c r="C19" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="32"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="s">
+      <c r="B18" s="67"/>
+      <c r="C18" s="57"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="47"/>
-      <c r="C20" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="32"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
+      <c r="B19" s="68"/>
+      <c r="C19" s="59"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="32"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
+      <c r="B20" s="67"/>
+      <c r="C20" s="57"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="32"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="32"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="32"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="32"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="32"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="32"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="32"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="59"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vGyDAsalwaZC+p9baMlFq+sGtzKRTptF3VR766UJ3xzwssuDLY56OVManIks/6lDInB2A1J8mgC93toF/gKOKw==" saltValue="V36fmNqkYOkMwr1EvtqK1w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -1553,59 +1458,59 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
       <c r="E1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" t="s">
-        <v>28</v>
-      </c>
       <c r="H1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="48">
+      <c r="A2" s="32">
         <v>20</v>
       </c>
-      <c r="B2" s="48">
+      <c r="B2" s="32">
         <v>0.95</v>
       </c>
-      <c r="C2" s="48">
+      <c r="C2" s="32">
         <v>0.85</v>
       </c>
-      <c r="D2" s="48">
+      <c r="D2" s="32">
         <v>1.1499999999999999</v>
       </c>
-      <c r="E2" s="48">
+      <c r="E2" s="32">
         <v>10</v>
       </c>
-      <c r="F2" s="48">
+      <c r="F2" s="32">
         <v>2.5</v>
       </c>
-      <c r="G2" s="48">
+      <c r="G2" s="32">
         <v>10</v>
       </c>
-      <c r="H2" s="48">
+      <c r="H2" s="32">
         <v>4.5</v>
       </c>
-      <c r="I2" s="48">
+      <c r="I2" s="32">
         <v>4.5</v>
       </c>
     </row>
@@ -1623,12 +1528,12 @@
   <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" style="4" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
     <col min="8" max="8" width="17.140625" customWidth="1"/>
     <col min="9" max="9" width="11.7109375" customWidth="1"/>
@@ -1638,563 +1543,643 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="36" t="s">
+      <c r="G1" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="H1" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="I1" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="J1" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="K1" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="L1" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="K1" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="L1" s="38" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="44"/>
+      <c r="A2" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="35"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="47"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" s="31"/>
+      <c r="L2" s="36"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="58"/>
+      <c r="A3" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="35"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="47"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" s="35"/>
+      <c r="L3" s="36"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="50"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="58"/>
+      <c r="A4" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="35"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="47"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="35"/>
+      <c r="L4" s="36"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="50"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="58"/>
+      <c r="A5" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="35"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="48"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="35"/>
+      <c r="L5" s="36"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="50"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="58"/>
+      <c r="A6" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="35"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="48"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="35"/>
+      <c r="L6" s="36"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="58"/>
+      <c r="A7" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="35"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="48"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="35"/>
+      <c r="L7" s="36"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="50"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="58"/>
+      <c r="A8" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="35"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="48"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" s="35"/>
+      <c r="L8" s="36"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="50"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="58"/>
+      <c r="A9" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="35"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="48"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="35"/>
+      <c r="L9" s="36"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="50"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="57"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="58"/>
+      <c r="A10" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="35"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="35"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="48"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="35"/>
+      <c r="L10" s="36"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="50"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="58"/>
+      <c r="A11" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="35"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="35"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="48"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" s="35"/>
+      <c r="L11" s="36"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
+      <c r="A24" s="1"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="18"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="21"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="15"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="13"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="22"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="18"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="16"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="22"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="18"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="16"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="22"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="18"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="16"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="22"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="18"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="22"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="18"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="16"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="22"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="18"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="16"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="22"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="18"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="16"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="22"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="18"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="16"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="22"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="18"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="16"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="25"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="13"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="11"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="25"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="13"/>
+      <c r="A39" s="23"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="11"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="25"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="14"/>
+      <c r="A40" s="23"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="12"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
+      <c r="A42" s="15"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="3"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
+      <c r="A46" s="1"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="3"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
+      <c r="A47" s="1"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
+      <c r="A48" s="1"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
+      <c r="A49" s="1"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="3"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
+      <c r="A50" s="1"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="3"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
+      <c r="A51" s="1"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="3"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
+      <c r="A52" s="1"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
+      <c r="A53" s="1"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="3"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
+      <c r="A54" s="1"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
+      <c r="A55" s="1"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="3"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
+      <c r="A56" s="1"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="3"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
+      <c r="A57" s="1"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="3"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
+      <c r="A58" s="1"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="3"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
+      <c r="A59" s="1"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="3"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
+      <c r="A60" s="1"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="3"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
+      <c r="A61" s="1"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="3"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
+      <c r="A62" s="1"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="3"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
+      <c r="A63" s="1"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="3"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
+      <c r="A64" s="1"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="3"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
+      <c r="A65" s="1"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="3"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
+      <c r="A66" s="1"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="3"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
+      <c r="A67" s="1"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="3"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
+      <c r="A68" s="1"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="3"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
+      <c r="A69" s="1"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="3"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
+      <c r="A70" s="1"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="3"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
+      <c r="A71" s="1"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="3"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
+      <c r="A72" s="1"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="3"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
+      <c r="A73" s="1"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="XveKTBQyAEmPMItSYehPiXBrhufHZdug/g135W2zalIaDMpIdH7KjwVijzCB76DPbzMIpZbiybUZsUqsn+XZrA==" saltValue="YHvyC4Lot0d//fu3QX+quQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
@@ -2213,777 +2198,746 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B151"/>
+  <dimension ref="A1:B148"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" style="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="40" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" style="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="str">
-        <f>INFO!B4</f>
-        <v>DxI 1 gefr</v>
-      </c>
-      <c r="B1" s="40" t="str">
-        <f>INFO!C4</f>
-        <v>DxI 2 gefr</v>
+      <c r="A1" s="30" t="str">
+        <f>INFO!B7</f>
+        <v>BNII</v>
+      </c>
+      <c r="B1" s="30" t="str">
+        <f>INFO!C7</f>
+        <v>AU5800</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="59">
-        <v>666.81</v>
-      </c>
-      <c r="B2" s="60">
-        <v>652.33000000000004</v>
+      <c r="A2" s="43">
+        <v>116</v>
+      </c>
+      <c r="B2" s="44">
+        <v>123.5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="61">
-        <v>737.41</v>
-      </c>
-      <c r="B3" s="62">
-        <v>706.03</v>
+      <c r="A3" s="41">
+        <v>99.1</v>
+      </c>
+      <c r="B3" s="42">
+        <v>95.8</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="59">
-        <v>285.04000000000002</v>
-      </c>
-      <c r="B4" s="60">
-        <v>268.7</v>
+      <c r="A4" s="43">
+        <v>156</v>
+      </c>
+      <c r="B4" s="44">
+        <v>188.9</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="61">
-        <v>259.02</v>
-      </c>
-      <c r="B5" s="62">
-        <v>265.07</v>
+      <c r="A5" s="41">
+        <v>241</v>
+      </c>
+      <c r="B5" s="42">
+        <v>240.6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="59">
-        <v>354.54</v>
-      </c>
-      <c r="B6" s="60">
-        <v>379.68</v>
+      <c r="A6" s="43">
+        <v>868</v>
+      </c>
+      <c r="B6" s="42">
+        <v>1238.9000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="61">
-        <v>332.28</v>
-      </c>
-      <c r="B7" s="62">
-        <v>346.54</v>
+      <c r="A7" s="43">
+        <v>217</v>
+      </c>
+      <c r="B7" s="42">
+        <v>278.5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="59">
-        <v>397.48</v>
-      </c>
-      <c r="B8" s="60">
-        <v>373.99</v>
+      <c r="A8" s="41">
+        <v>104</v>
+      </c>
+      <c r="B8" s="44">
+        <v>84.8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="61">
-        <v>4173.42</v>
-      </c>
-      <c r="B9" s="62">
-        <v>4092.78</v>
+      <c r="A9" s="43">
+        <v>29.8</v>
+      </c>
+      <c r="B9" s="42">
+        <v>15.6</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="59">
-        <v>366.15</v>
-      </c>
-      <c r="B10" s="60">
-        <v>356.28</v>
+      <c r="A10" s="41">
+        <v>768</v>
+      </c>
+      <c r="B10" s="44">
+        <v>974.1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="61">
-        <v>177.08</v>
-      </c>
-      <c r="B11" s="62">
-        <v>190.91</v>
+      <c r="A11" s="43">
+        <v>1290</v>
+      </c>
+      <c r="B11" s="42">
+        <v>1612</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="59">
-        <v>374.59</v>
-      </c>
-      <c r="B12" s="60">
-        <v>384.91</v>
+      <c r="A12" s="41">
+        <v>465</v>
+      </c>
+      <c r="B12" s="44">
+        <v>632.6</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="61">
-        <v>265.08</v>
-      </c>
-      <c r="B13" s="62">
-        <v>286.31</v>
+      <c r="A13" s="43">
+        <v>470</v>
+      </c>
+      <c r="B13" s="42">
+        <v>815.9</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="59">
-        <v>533.20000000000005</v>
-      </c>
-      <c r="B14" s="60">
-        <v>575.71</v>
+      <c r="A14" s="41">
+        <v>1700</v>
+      </c>
+      <c r="B14" s="44">
+        <v>2182</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="61">
-        <v>468.68</v>
-      </c>
-      <c r="B15" s="62">
-        <v>491.59</v>
+      <c r="A15" s="43">
+        <v>31.1</v>
+      </c>
+      <c r="B15" s="42">
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="59">
-        <v>361.53</v>
-      </c>
-      <c r="B16" s="60">
-        <v>373.23</v>
+      <c r="A16" s="43">
+        <v>72.2</v>
+      </c>
+      <c r="B16" s="42">
+        <v>64.900000000000006</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="61">
-        <v>208.55</v>
-      </c>
-      <c r="B17" s="62">
-        <v>231.72</v>
+      <c r="A17" s="41">
+        <v>119</v>
+      </c>
+      <c r="B17" s="44">
+        <v>121.8</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="59">
-        <v>454.81</v>
-      </c>
-      <c r="B18" s="60">
-        <v>454.81</v>
+      <c r="A18" s="43">
+        <v>415</v>
+      </c>
+      <c r="B18" s="42">
+        <v>782.2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="61">
-        <v>303.45999999999998</v>
-      </c>
-      <c r="B19" s="62">
-        <v>307.85000000000002</v>
+      <c r="A19" s="41">
+        <v>145</v>
+      </c>
+      <c r="B19" s="44">
+        <v>180.2</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="59">
-        <v>158.56</v>
-      </c>
-      <c r="B20" s="60">
-        <v>163.28</v>
+      <c r="A20" s="43">
+        <v>183</v>
+      </c>
+      <c r="B20" s="42">
+        <v>186.4</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="61">
-        <v>637.58000000000004</v>
-      </c>
-      <c r="B21" s="62">
-        <v>635.41</v>
+      <c r="A21" s="41">
+        <v>363</v>
+      </c>
+      <c r="B21" s="44">
+        <v>420.9</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="59">
-        <v>390.08</v>
-      </c>
-      <c r="B22" s="60">
-        <v>403.68</v>
+      <c r="A22" s="43">
+        <v>500</v>
+      </c>
+      <c r="B22" s="42">
+        <v>642.25</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="61">
-        <v>918.35</v>
-      </c>
-      <c r="B23" s="62">
-        <v>1009.91</v>
+      <c r="A23" s="43">
+        <v>682</v>
+      </c>
+      <c r="B23" s="42">
+        <v>875.61</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="59">
-        <v>252.2</v>
-      </c>
-      <c r="B24" s="60">
-        <v>268.88</v>
+      <c r="A24" s="46">
+        <v>881</v>
+      </c>
+      <c r="B24" s="46">
+        <v>1016</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="61">
-        <v>923.19</v>
-      </c>
-      <c r="B25" s="62">
-        <v>1006.38</v>
+      <c r="A25" s="46">
+        <v>634</v>
+      </c>
+      <c r="B25" s="46">
+        <v>809</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="59">
-        <v>1625.54</v>
-      </c>
-      <c r="B26" s="60">
-        <v>1588.88</v>
+      <c r="A26" s="46">
+        <v>312</v>
+      </c>
+      <c r="B26" s="46">
+        <v>363</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="61">
-        <v>584.19000000000005</v>
-      </c>
-      <c r="B27" s="62">
-        <v>612.5</v>
+      <c r="A27" s="41">
+        <v>1290</v>
+      </c>
+      <c r="B27" s="44">
+        <v>2080.88</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="59">
-        <v>633.16</v>
-      </c>
-      <c r="B28" s="60">
-        <v>715.79</v>
+      <c r="A28" s="43">
+        <v>98.2</v>
+      </c>
+      <c r="B28" s="42">
+        <v>83.5</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="61">
-        <v>760.45</v>
-      </c>
-      <c r="B29" s="62">
-        <v>806.27</v>
+      <c r="A29" s="41">
+        <v>180</v>
+      </c>
+      <c r="B29" s="44">
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="59">
-        <v>207.42</v>
-      </c>
-      <c r="B30" s="60">
-        <v>215.8</v>
+      <c r="A30" s="43">
+        <v>57.9</v>
+      </c>
+      <c r="B30" s="42">
+        <v>68.900000000000006</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="61">
-        <v>336.36</v>
-      </c>
-      <c r="B31" s="62">
-        <v>382.68</v>
+      <c r="A31" s="41">
+        <v>59.8</v>
+      </c>
+      <c r="B31" s="44">
+        <v>65.099999999999994</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="59">
-        <v>975.91</v>
-      </c>
-      <c r="B32" s="60">
-        <v>1029.75</v>
+      <c r="A32" s="41">
+        <v>62.7</v>
+      </c>
+      <c r="B32" s="44">
+        <v>51.2</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="61">
-        <v>312.49</v>
-      </c>
-      <c r="B33" s="62">
-        <v>354.69</v>
+      <c r="A33" s="43">
+        <v>511</v>
+      </c>
+      <c r="B33" s="42">
+        <v>537.5</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="59">
-        <v>225.56</v>
-      </c>
-      <c r="B34" s="60">
-        <v>250.62</v>
+      <c r="A34" s="41">
+        <v>667</v>
+      </c>
+      <c r="B34" s="44">
+        <v>770.9</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="61">
-        <v>542.03</v>
-      </c>
-      <c r="B35" s="62">
-        <v>612.71</v>
-      </c>
+      <c r="A35" s="43"/>
+      <c r="B35" s="42"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="59">
-        <v>699.69</v>
-      </c>
-      <c r="B36" s="60">
-        <v>752.42</v>
-      </c>
+      <c r="A36" s="41"/>
+      <c r="B36" s="44"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="61">
-        <v>390.22</v>
-      </c>
-      <c r="B37" s="62">
-        <v>438.28</v>
-      </c>
+      <c r="A37" s="43"/>
+      <c r="B37" s="42"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="59">
-        <v>414.34</v>
-      </c>
-      <c r="B38" s="60">
-        <v>431.32</v>
-      </c>
+      <c r="A38" s="46"/>
+      <c r="B38" s="44"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="61">
-        <v>98.14</v>
-      </c>
-      <c r="B39" s="62">
-        <v>101.19</v>
-      </c>
+      <c r="A39" s="43"/>
+      <c r="B39" s="44"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="59"/>
-      <c r="B40" s="60"/>
+      <c r="A40" s="41"/>
+      <c r="B40" s="42"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="61"/>
-      <c r="B41" s="62"/>
+      <c r="A41" s="43"/>
+      <c r="B41" s="44"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="59"/>
-      <c r="B42" s="60"/>
+      <c r="A42" s="41"/>
+      <c r="B42" s="42"/>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="61"/>
-      <c r="B43" s="62"/>
+      <c r="A43" s="43"/>
+      <c r="B43" s="44"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="59"/>
-      <c r="B44" s="60"/>
+      <c r="A44" s="41"/>
+      <c r="B44" s="42"/>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="61"/>
-      <c r="B45" s="62"/>
+      <c r="A45" s="41"/>
+      <c r="B45" s="42"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="59"/>
-      <c r="B46" s="60"/>
+      <c r="A46" s="43"/>
+      <c r="B46" s="44"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="61"/>
-      <c r="B47" s="62"/>
+      <c r="A47" s="41"/>
+      <c r="B47" s="42"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="59"/>
-      <c r="B48" s="60"/>
+      <c r="A48" s="43"/>
+      <c r="B48" s="44"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="61"/>
-      <c r="B49" s="62"/>
+      <c r="A49" s="41"/>
+      <c r="B49" s="42"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="59"/>
-      <c r="B50" s="60"/>
+      <c r="A50" s="43"/>
+      <c r="B50" s="44"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="61"/>
-      <c r="B51" s="62"/>
+      <c r="A51" s="41"/>
+      <c r="B51" s="42"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="59"/>
-      <c r="B52" s="60"/>
+      <c r="A52" s="43"/>
+      <c r="B52" s="44"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="61"/>
-      <c r="B53" s="62"/>
+      <c r="A53" s="41"/>
+      <c r="B53" s="42"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="59"/>
-      <c r="B54" s="60"/>
+      <c r="A54" s="43"/>
+      <c r="B54" s="44"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="61"/>
-      <c r="B55" s="62"/>
+      <c r="A55" s="41"/>
+      <c r="B55" s="42"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="59"/>
-      <c r="B56" s="60"/>
+      <c r="A56" s="43"/>
+      <c r="B56" s="44"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="61"/>
-      <c r="B57" s="62"/>
+      <c r="A57" s="41"/>
+      <c r="B57" s="42"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="59"/>
-      <c r="B58" s="60"/>
+      <c r="A58" s="43"/>
+      <c r="B58" s="44"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="61"/>
-      <c r="B59" s="62"/>
+      <c r="A59" s="41"/>
+      <c r="B59" s="42"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="59"/>
-      <c r="B60" s="60"/>
+      <c r="A60" s="43"/>
+      <c r="B60" s="44"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="61"/>
-      <c r="B61" s="62"/>
+      <c r="A61" s="41"/>
+      <c r="B61" s="42"/>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="59"/>
-      <c r="B62" s="60"/>
+      <c r="A62" s="43"/>
+      <c r="B62" s="44"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="61"/>
-      <c r="B63" s="62"/>
+      <c r="A63" s="41"/>
+      <c r="B63" s="42"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="59"/>
-      <c r="B64" s="60"/>
+      <c r="A64" s="43"/>
+      <c r="B64" s="44"/>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="61"/>
-      <c r="B65" s="62"/>
+      <c r="A65" s="41"/>
+      <c r="B65" s="42"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="59"/>
-      <c r="B66" s="60"/>
+      <c r="A66" s="43"/>
+      <c r="B66" s="44"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="61"/>
-      <c r="B67" s="62"/>
+      <c r="A67" s="41"/>
+      <c r="B67" s="42"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="59"/>
-      <c r="B68" s="60"/>
+      <c r="A68" s="43"/>
+      <c r="B68" s="44"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="61"/>
-      <c r="B69" s="62"/>
+      <c r="A69" s="41"/>
+      <c r="B69" s="42"/>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="59"/>
-      <c r="B70" s="60"/>
+      <c r="A70" s="43"/>
+      <c r="B70" s="44"/>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="61"/>
-      <c r="B71" s="62"/>
+      <c r="A71" s="41"/>
+      <c r="B71" s="42"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="59"/>
-      <c r="B72" s="60"/>
+      <c r="A72" s="43"/>
+      <c r="B72" s="44"/>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="61"/>
-      <c r="B73" s="62"/>
+      <c r="A73" s="41"/>
+      <c r="B73" s="42"/>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="59"/>
-      <c r="B74" s="60"/>
+      <c r="A74" s="43"/>
+      <c r="B74" s="44"/>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="61"/>
-      <c r="B75" s="62"/>
+      <c r="A75" s="41"/>
+      <c r="B75" s="42"/>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="59"/>
-      <c r="B76" s="60"/>
+      <c r="A76" s="43"/>
+      <c r="B76" s="44"/>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="61"/>
-      <c r="B77" s="62"/>
+      <c r="A77" s="41"/>
+      <c r="B77" s="42"/>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="59"/>
-      <c r="B78" s="60"/>
+      <c r="A78" s="43"/>
+      <c r="B78" s="44"/>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="61"/>
-      <c r="B79" s="62"/>
+      <c r="A79" s="41"/>
+      <c r="B79" s="42"/>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="59"/>
-      <c r="B80" s="60"/>
+      <c r="A80" s="43"/>
+      <c r="B80" s="44"/>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="61"/>
-      <c r="B81" s="62"/>
+      <c r="A81" s="41"/>
+      <c r="B81" s="42"/>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="59"/>
-      <c r="B82" s="60"/>
+      <c r="A82" s="43"/>
+      <c r="B82" s="44"/>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="61"/>
-      <c r="B83" s="62"/>
+      <c r="A83" s="41"/>
+      <c r="B83" s="42"/>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="59"/>
-      <c r="B84" s="60"/>
+      <c r="A84" s="43"/>
+      <c r="B84" s="44"/>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="61"/>
-      <c r="B85" s="62"/>
+      <c r="A85" s="41"/>
+      <c r="B85" s="42"/>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="59"/>
-      <c r="B86" s="60"/>
+      <c r="A86" s="43"/>
+      <c r="B86" s="44"/>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="61"/>
-      <c r="B87" s="62"/>
+      <c r="A87" s="41"/>
+      <c r="B87" s="42"/>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="59"/>
-      <c r="B88" s="60"/>
+      <c r="A88" s="43"/>
+      <c r="B88" s="44"/>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="61"/>
-      <c r="B89" s="62"/>
+      <c r="A89" s="41"/>
+      <c r="B89" s="42"/>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="59"/>
-      <c r="B90" s="60"/>
+      <c r="A90" s="43"/>
+      <c r="B90" s="44"/>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="61"/>
-      <c r="B91" s="62"/>
+      <c r="A91" s="41"/>
+      <c r="B91" s="42"/>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="59"/>
-      <c r="B92" s="60"/>
+      <c r="A92" s="43"/>
+      <c r="B92" s="44"/>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="61"/>
-      <c r="B93" s="62"/>
+      <c r="A93" s="41"/>
+      <c r="B93" s="42"/>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="59"/>
-      <c r="B94" s="60"/>
+      <c r="A94" s="43"/>
+      <c r="B94" s="44"/>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="61"/>
-      <c r="B95" s="62"/>
+      <c r="A95" s="41"/>
+      <c r="B95" s="42"/>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="59"/>
-      <c r="B96" s="60"/>
+      <c r="A96" s="43"/>
+      <c r="B96" s="44"/>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="61"/>
-      <c r="B97" s="62"/>
+      <c r="A97" s="41"/>
+      <c r="B97" s="42"/>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="59"/>
-      <c r="B98" s="60"/>
+      <c r="A98" s="43"/>
+      <c r="B98" s="44"/>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="61"/>
-      <c r="B99" s="62"/>
+      <c r="A99" s="41"/>
+      <c r="B99" s="42"/>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="59"/>
-      <c r="B100" s="60"/>
+      <c r="A100" s="43"/>
+      <c r="B100" s="44"/>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="61"/>
-      <c r="B101" s="62"/>
+      <c r="A101" s="41"/>
+      <c r="B101" s="42"/>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="59"/>
-      <c r="B102" s="60"/>
+      <c r="A102" s="43"/>
+      <c r="B102" s="44"/>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="61"/>
-      <c r="B103" s="62"/>
+      <c r="A103" s="41"/>
+      <c r="B103" s="42"/>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="59"/>
-      <c r="B104" s="60"/>
+      <c r="A104" s="43"/>
+      <c r="B104" s="44"/>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="61"/>
-      <c r="B105" s="62"/>
+      <c r="A105" s="41"/>
+      <c r="B105" s="42"/>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="59"/>
-      <c r="B106" s="60"/>
+      <c r="A106" s="43"/>
+      <c r="B106" s="44"/>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="61"/>
-      <c r="B107" s="62"/>
+      <c r="A107" s="41"/>
+      <c r="B107" s="42"/>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="59"/>
-      <c r="B108" s="60"/>
+      <c r="A108" s="43"/>
+      <c r="B108" s="44"/>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="61"/>
-      <c r="B109" s="62"/>
+      <c r="A109" s="41"/>
+      <c r="B109" s="42"/>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="59"/>
-      <c r="B110" s="60"/>
+      <c r="A110" s="43"/>
+      <c r="B110" s="44"/>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" s="61"/>
-      <c r="B111" s="62"/>
+      <c r="A111" s="41"/>
+      <c r="B111" s="42"/>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="59"/>
-      <c r="B112" s="60"/>
+      <c r="A112" s="43"/>
+      <c r="B112" s="44"/>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="61"/>
-      <c r="B113" s="62"/>
+      <c r="A113" s="41"/>
+      <c r="B113" s="42"/>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="59"/>
-      <c r="B114" s="60"/>
+      <c r="A114" s="43"/>
+      <c r="B114" s="44"/>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="61"/>
-      <c r="B115" s="62"/>
+      <c r="A115" s="41"/>
+      <c r="B115" s="42"/>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="59"/>
-      <c r="B116" s="60"/>
+      <c r="A116" s="43"/>
+      <c r="B116" s="44"/>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="61"/>
-      <c r="B117" s="62"/>
+      <c r="A117" s="41"/>
+      <c r="B117" s="42"/>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="59"/>
-      <c r="B118" s="60"/>
+      <c r="A118" s="43"/>
+      <c r="B118" s="44"/>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="61"/>
-      <c r="B119" s="62"/>
+      <c r="A119" s="41"/>
+      <c r="B119" s="42"/>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="59"/>
-      <c r="B120" s="60"/>
+      <c r="A120" s="43"/>
+      <c r="B120" s="44"/>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="61"/>
-      <c r="B121" s="62"/>
+      <c r="A121" s="41"/>
+      <c r="B121" s="42"/>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="59"/>
-      <c r="B122" s="60"/>
+      <c r="A122" s="43"/>
+      <c r="B122" s="44"/>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="61"/>
-      <c r="B123" s="62"/>
+      <c r="A123" s="41"/>
+      <c r="B123" s="42"/>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="59"/>
-      <c r="B124" s="60"/>
+      <c r="A124" s="43"/>
+      <c r="B124" s="44"/>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="61"/>
-      <c r="B125" s="62"/>
+      <c r="A125" s="41"/>
+      <c r="B125" s="42"/>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="59"/>
-      <c r="B126" s="60"/>
+      <c r="A126" s="43"/>
+      <c r="B126" s="44"/>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="61"/>
-      <c r="B127" s="62"/>
+      <c r="A127" s="41"/>
+      <c r="B127" s="42"/>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="59"/>
-      <c r="B128" s="60"/>
+      <c r="A128" s="43"/>
+      <c r="B128" s="44"/>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="61"/>
-      <c r="B129" s="62"/>
+      <c r="A129" s="41"/>
+      <c r="B129" s="42"/>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="59"/>
-      <c r="B130" s="60"/>
+      <c r="A130" s="43"/>
+      <c r="B130" s="44"/>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="61"/>
-      <c r="B131" s="62"/>
+      <c r="A131" s="41"/>
+      <c r="B131" s="42"/>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="59"/>
-      <c r="B132" s="60"/>
+      <c r="A132" s="43"/>
+      <c r="B132" s="44"/>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="61"/>
-      <c r="B133" s="62"/>
+      <c r="A133" s="41"/>
+      <c r="B133" s="42"/>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="59"/>
-      <c r="B134" s="60"/>
+      <c r="A134" s="43"/>
+      <c r="B134" s="44"/>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="61"/>
-      <c r="B135" s="62"/>
+      <c r="A135" s="41"/>
+      <c r="B135" s="42"/>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" s="59"/>
-      <c r="B136" s="60"/>
+      <c r="A136" s="43"/>
+      <c r="B136" s="44"/>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" s="61"/>
-      <c r="B137" s="62"/>
+      <c r="A137" s="41"/>
+      <c r="B137" s="42"/>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" s="59"/>
-      <c r="B138" s="60"/>
+      <c r="A138" s="43"/>
+      <c r="B138" s="44"/>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" s="61"/>
-      <c r="B139" s="62"/>
+      <c r="A139" s="41"/>
+      <c r="B139" s="42"/>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" s="59"/>
-      <c r="B140" s="60"/>
+      <c r="A140" s="43"/>
+      <c r="B140" s="44"/>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="61"/>
-      <c r="B141" s="62"/>
+      <c r="A141" s="41"/>
+      <c r="B141" s="42"/>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="59"/>
-      <c r="B142" s="60"/>
+      <c r="A142" s="43"/>
+      <c r="B142" s="44"/>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" s="61"/>
-      <c r="B143" s="62"/>
+      <c r="A143" s="41"/>
+      <c r="B143" s="42"/>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" s="59"/>
-      <c r="B144" s="60"/>
+      <c r="A144" s="43"/>
+      <c r="B144" s="44"/>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" s="61"/>
-      <c r="B145" s="62"/>
+      <c r="A145" s="41"/>
+      <c r="B145" s="42"/>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" s="59"/>
-      <c r="B146" s="60"/>
+      <c r="A146" s="43"/>
+      <c r="B146" s="44"/>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" s="61"/>
-      <c r="B147" s="62"/>
+      <c r="A147" s="41"/>
+      <c r="B147" s="42"/>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" s="59"/>
-      <c r="B148" s="60"/>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" s="61"/>
-      <c r="B149" s="62"/>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" s="59"/>
-      <c r="B150" s="60"/>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" s="63"/>
-      <c r="B151" s="49"/>
+      <c r="A148" s="45"/>
+      <c r="B148" s="33"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="r1ykXqBIcJKhUGg0U0y0EXiBs/Ub1K5e17tQNniAOr5azn9tVVxI8k3sT+73Mkr6ZYhRJDSyaNpoEp25U41Qbg==" saltValue="+y6Ah40QkzJQ8wxf6wyVbA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/vdata.xlsx
+++ b/vdata.xlsx
@@ -9,13 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18780" windowHeight="7080"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18780" windowHeight="7080" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="INFO" sheetId="9" r:id="rId1"/>
     <sheet name="CRIT" sheetId="5" r:id="rId2"/>
     <sheet name="PREC" sheetId="8" r:id="rId3"/>
     <sheet name="DATA" sheetId="1" r:id="rId4"/>
+    <sheet name="PREC25" sheetId="11" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="70">
   <si>
     <t>Projekt</t>
   </si>
@@ -161,66 +162,6 @@
     <t>ZLM</t>
   </si>
   <si>
-    <t>07.08.23/AU1</t>
-  </si>
-  <si>
-    <t>08.08.23/AU1</t>
-  </si>
-  <si>
-    <t>09.08.23/AU1</t>
-  </si>
-  <si>
-    <t>10.08.23/AU1</t>
-  </si>
-  <si>
-    <t>11.08.23/AU1</t>
-  </si>
-  <si>
-    <t>12.08.23/AU1</t>
-  </si>
-  <si>
-    <t>13.08.23/AU1</t>
-  </si>
-  <si>
-    <t>10.09.23/AU1</t>
-  </si>
-  <si>
-    <t>12.09.23/AU1</t>
-  </si>
-  <si>
-    <t>13.09.23/AU1</t>
-  </si>
-  <si>
-    <t>07.08.23/AU2</t>
-  </si>
-  <si>
-    <t>08.08.23/AU2</t>
-  </si>
-  <si>
-    <t>09.08.23/AU2</t>
-  </si>
-  <si>
-    <t>10.08.23/AU2</t>
-  </si>
-  <si>
-    <t>11.08.23/AU2</t>
-  </si>
-  <si>
-    <t>12.08.23/AU2</t>
-  </si>
-  <si>
-    <t>13.08.23/AU2</t>
-  </si>
-  <si>
-    <t>10.09.23/AU2</t>
-  </si>
-  <si>
-    <t>12.09.23/AU2</t>
-  </si>
-  <si>
-    <t>13.09.23/AU2</t>
-  </si>
-  <si>
     <t>g/L</t>
   </si>
   <si>
@@ -245,10 +186,58 @@
     <t>Feb/Mrz 2024</t>
   </si>
   <si>
-    <t>ApoB Nephelometrie</t>
-  </si>
-  <si>
-    <t>Lp(a)</t>
+    <t>Nephelometrie</t>
+  </si>
+  <si>
+    <t>Lp(a) BNII</t>
+  </si>
+  <si>
+    <t>Lp(a) AU</t>
+  </si>
+  <si>
+    <t>L1 Aliquot 1</t>
+  </si>
+  <si>
+    <t>L1 Aliquot 2</t>
+  </si>
+  <si>
+    <t>L1 Aliquot 3</t>
+  </si>
+  <si>
+    <t>L1 Aliquot 4</t>
+  </si>
+  <si>
+    <t>L1 Aliquot 5</t>
+  </si>
+  <si>
+    <t>L2 Aliquot 1</t>
+  </si>
+  <si>
+    <t>L2 Aliquot 2</t>
+  </si>
+  <si>
+    <t>L2 Aliquot 3</t>
+  </si>
+  <si>
+    <t>L2 Aliquot 4</t>
+  </si>
+  <si>
+    <t>L2 Aliquot 5</t>
+  </si>
+  <si>
+    <t>d1</t>
+  </si>
+  <si>
+    <t>d2</t>
+  </si>
+  <si>
+    <t>d3</t>
+  </si>
+  <si>
+    <t>d4</t>
+  </si>
+  <si>
+    <t>d5</t>
   </si>
 </sst>
 </file>
@@ -302,7 +291,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -333,8 +322,14 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -448,11 +443,113 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -584,10 +681,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -644,6 +737,36 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1246,195 +1369,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" customWidth="1"/>
+    <col min="3" max="3" width="30.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="B1" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="56" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="B2" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="58" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="56" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="58" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="58" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="50" t="s">
+      <c r="B5" s="57" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="56" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="s">
+      <c r="B6" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="56" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="58" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="59" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="50" t="s">
+      <c r="B7" s="57" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="57"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="51" t="s">
+      <c r="B8" s="59"/>
+      <c r="C8" s="56"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="62"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="50" t="s">
+      <c r="B9" s="60"/>
+      <c r="C9" s="61"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="63"/>
-      <c r="C10" s="64"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="52" t="s">
+      <c r="B10" s="62"/>
+      <c r="C10" s="63"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="65"/>
-      <c r="C11" s="62"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="50" t="s">
+      <c r="B11" s="64"/>
+      <c r="C11" s="61"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="57" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="51" t="s">
+      <c r="B12" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="56" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+      <c r="B13" s="58"/>
+      <c r="C13" s="58"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="57"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="53" t="s">
+      <c r="B14" s="55"/>
+      <c r="C14" s="56"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="59"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="50" t="s">
+      <c r="B15" s="57"/>
+      <c r="C15" s="58"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="69" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="69" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="53" t="s">
+      <c r="B16" s="68" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="68" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="59"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="50" t="s">
+      <c r="B17" s="65"/>
+      <c r="C17" s="58"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="67"/>
-      <c r="C18" s="57"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="51" t="s">
+      <c r="B18" s="66"/>
+      <c r="C18" s="56"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="68"/>
-      <c r="C19" s="59"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="50" t="s">
+      <c r="B19" s="67"/>
+      <c r="C19" s="58"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="67"/>
-      <c r="C20" s="57"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="51" t="s">
+      <c r="B20" s="66"/>
+      <c r="C20" s="56"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="65"/>
-      <c r="C21" s="59"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="58"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1444,19 +1567,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.26953125" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7265625" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -1485,7 +1608,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="32">
         <v>20</v>
       </c>
@@ -1526,23 +1649,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" customWidth="1"/>
-    <col min="11" max="11" width="17.140625" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="17.1796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.1796875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" customWidth="1"/>
+    <col min="9" max="9" width="11.7265625" customWidth="1"/>
+    <col min="10" max="10" width="14.54296875" customWidth="1"/>
+    <col min="11" max="11" width="17.1796875" customWidth="1"/>
+    <col min="12" max="12" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="s">
         <v>29</v>
       </c>
@@ -1580,232 +1703,392 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="35"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="47"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="K2" s="31"/>
-      <c r="L2" s="36"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="35"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="47"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="K3" s="35"/>
-      <c r="L3" s="36"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="35"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="47"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="K4" s="35"/>
-      <c r="L4" s="36"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="35"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" s="48"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" s="35"/>
-      <c r="L5" s="36"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="35"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="48"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" s="35"/>
-      <c r="L6" s="36"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="35"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="K7" s="35"/>
-      <c r="L7" s="36"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="35"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="48"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="K8" s="35"/>
-      <c r="L8" s="36"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="35"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="48"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" s="35"/>
-      <c r="L9" s="36"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="35"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10" s="48"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="K10" s="35"/>
-      <c r="L10" s="36"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="48"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="K11" s="35"/>
-      <c r="L11" s="36"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="34">
+        <v>45396</v>
+      </c>
+      <c r="B2" s="35">
+        <v>22.46</v>
+      </c>
+      <c r="C2" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="D2" s="37">
+        <v>45396</v>
+      </c>
+      <c r="E2" s="35">
+        <v>53.09</v>
+      </c>
+      <c r="F2" s="36">
+        <v>51.7</v>
+      </c>
+      <c r="G2" s="38">
+        <v>45396</v>
+      </c>
+      <c r="H2" s="46">
+        <v>21.05</v>
+      </c>
+      <c r="I2" s="39">
+        <v>22.5</v>
+      </c>
+      <c r="J2" s="38">
+        <v>45396</v>
+      </c>
+      <c r="K2" s="31">
+        <v>54.35</v>
+      </c>
+      <c r="L2" s="36">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="34">
+        <v>45396</v>
+      </c>
+      <c r="B3" s="35">
+        <v>23.31</v>
+      </c>
+      <c r="C3" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="D3" s="37">
+        <v>45397</v>
+      </c>
+      <c r="E3" s="35">
+        <v>54.41</v>
+      </c>
+      <c r="F3" s="36">
+        <v>51.7</v>
+      </c>
+      <c r="G3" s="40">
+        <v>45396</v>
+      </c>
+      <c r="H3" s="46">
+        <v>26.6</v>
+      </c>
+      <c r="I3" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="J3" s="40">
+        <v>45397</v>
+      </c>
+      <c r="K3" s="35">
+        <v>56.62</v>
+      </c>
+      <c r="L3" s="36">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="34">
+        <v>45396</v>
+      </c>
+      <c r="B4" s="35">
+        <v>21.05</v>
+      </c>
+      <c r="C4" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="D4" s="37">
+        <v>45398</v>
+      </c>
+      <c r="E4" s="35">
+        <v>54.35</v>
+      </c>
+      <c r="F4" s="36">
+        <v>51.7</v>
+      </c>
+      <c r="G4" s="40">
+        <v>45396</v>
+      </c>
+      <c r="H4" s="46">
+        <v>23.33</v>
+      </c>
+      <c r="I4" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="J4" s="40">
+        <v>45398</v>
+      </c>
+      <c r="K4" s="35">
+        <v>54.16</v>
+      </c>
+      <c r="L4" s="36">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="34">
+        <v>45396</v>
+      </c>
+      <c r="B5" s="35">
+        <v>23.52</v>
+      </c>
+      <c r="C5" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="D5" s="37">
+        <v>45399</v>
+      </c>
+      <c r="E5" s="35">
+        <v>54.09</v>
+      </c>
+      <c r="F5" s="36">
+        <v>51.7</v>
+      </c>
+      <c r="G5" s="40">
+        <v>45396</v>
+      </c>
+      <c r="H5" s="47">
+        <v>23.2</v>
+      </c>
+      <c r="I5" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="J5" s="40">
+        <v>45399</v>
+      </c>
+      <c r="K5" s="35">
+        <v>55.33</v>
+      </c>
+      <c r="L5" s="36">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="34">
+        <v>45396</v>
+      </c>
+      <c r="B6" s="35">
+        <v>22.21</v>
+      </c>
+      <c r="C6" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="D6" s="37">
+        <v>45400</v>
+      </c>
+      <c r="E6" s="35">
+        <v>53.99</v>
+      </c>
+      <c r="F6" s="36">
+        <v>51.7</v>
+      </c>
+      <c r="G6" s="40">
+        <v>45396</v>
+      </c>
+      <c r="H6" s="47">
+        <v>26.64</v>
+      </c>
+      <c r="I6" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="J6" s="40">
+        <v>45400</v>
+      </c>
+      <c r="K6" s="35">
+        <v>55.45</v>
+      </c>
+      <c r="L6" s="36">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="34">
+        <v>45397</v>
+      </c>
+      <c r="B7" s="35">
+        <v>23.7</v>
+      </c>
+      <c r="C7" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="D7" s="37">
+        <v>45396</v>
+      </c>
+      <c r="E7" s="35">
+        <v>56.42</v>
+      </c>
+      <c r="F7" s="36">
+        <v>51.7</v>
+      </c>
+      <c r="G7" s="40">
+        <v>45397</v>
+      </c>
+      <c r="H7" s="47">
+        <v>23.52</v>
+      </c>
+      <c r="I7" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="J7" s="40">
+        <v>45396</v>
+      </c>
+      <c r="K7" s="35">
+        <v>54.09</v>
+      </c>
+      <c r="L7" s="36">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="34">
+        <v>45397</v>
+      </c>
+      <c r="B8" s="35">
+        <v>22.3</v>
+      </c>
+      <c r="C8" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="D8" s="37">
+        <v>45397</v>
+      </c>
+      <c r="E8" s="35">
+        <v>54.53</v>
+      </c>
+      <c r="F8" s="36">
+        <v>51.7</v>
+      </c>
+      <c r="G8" s="40">
+        <v>45397</v>
+      </c>
+      <c r="H8" s="47">
+        <v>23.58</v>
+      </c>
+      <c r="I8" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="J8" s="40">
+        <v>45397</v>
+      </c>
+      <c r="K8" s="35">
+        <v>56.15</v>
+      </c>
+      <c r="L8" s="36">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="34">
+        <v>45397</v>
+      </c>
+      <c r="B9" s="35">
+        <v>26.6</v>
+      </c>
+      <c r="C9" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="D9" s="37">
+        <v>45398</v>
+      </c>
+      <c r="E9" s="35">
+        <v>56.62</v>
+      </c>
+      <c r="F9" s="36">
+        <v>51.7</v>
+      </c>
+      <c r="G9" s="40">
+        <v>45397</v>
+      </c>
+      <c r="H9" s="47">
+        <v>22.92</v>
+      </c>
+      <c r="I9" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="J9" s="40">
+        <v>45398</v>
+      </c>
+      <c r="K9" s="35">
+        <v>55.54</v>
+      </c>
+      <c r="L9" s="36">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="34">
+        <v>45397</v>
+      </c>
+      <c r="B10" s="35">
+        <v>23.58</v>
+      </c>
+      <c r="C10" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="D10" s="37">
+        <v>45399</v>
+      </c>
+      <c r="E10" s="35">
+        <v>56.15</v>
+      </c>
+      <c r="F10" s="36">
+        <v>51.7</v>
+      </c>
+      <c r="G10" s="40">
+        <v>45397</v>
+      </c>
+      <c r="H10" s="47">
+        <v>23.26</v>
+      </c>
+      <c r="I10" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="J10" s="40">
+        <v>45399</v>
+      </c>
+      <c r="K10" s="35">
+        <v>54.76</v>
+      </c>
+      <c r="L10" s="36">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="34">
+        <v>45397</v>
+      </c>
+      <c r="B11" s="35">
+        <v>24.73</v>
+      </c>
+      <c r="C11" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="D11" s="37">
+        <v>45400</v>
+      </c>
+      <c r="E11" s="35">
+        <v>56.33</v>
+      </c>
+      <c r="F11" s="36">
+        <v>51.7</v>
+      </c>
+      <c r="G11" s="40">
+        <v>45397</v>
+      </c>
+      <c r="H11" s="47">
+        <v>25.63</v>
+      </c>
+      <c r="I11" s="36">
+        <v>22.5</v>
+      </c>
+      <c r="J11" s="40">
+        <v>45400</v>
+      </c>
+      <c r="K11" s="35">
+        <v>56.3</v>
+      </c>
+      <c r="L11" s="36">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -1813,7 +2096,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="8"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1821,7 +2104,7 @@
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="17"/>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
@@ -1829,7 +2112,7 @@
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="19"/>
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
@@ -1837,7 +2120,7 @@
       <c r="E27" s="19"/>
       <c r="F27" s="19"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="22"/>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -1845,7 +2128,7 @@
       <c r="E28" s="21"/>
       <c r="F28" s="13"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="20"/>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -1853,7 +2136,7 @@
       <c r="E29" s="20"/>
       <c r="F29" s="16"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="20"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -1861,7 +2144,7 @@
       <c r="E30" s="20"/>
       <c r="F30" s="16"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="20"/>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -1869,7 +2152,7 @@
       <c r="E31" s="20"/>
       <c r="F31" s="16"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="20"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -1877,7 +2160,7 @@
       <c r="E32" s="20"/>
       <c r="F32" s="16"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="20"/>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -1885,7 +2168,7 @@
       <c r="E33" s="20"/>
       <c r="F33" s="16"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="20"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -1893,7 +2176,7 @@
       <c r="E34" s="20"/>
       <c r="F34" s="16"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="20"/>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -1901,7 +2184,7 @@
       <c r="E35" s="20"/>
       <c r="F35" s="16"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="20"/>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -1909,7 +2192,7 @@
       <c r="E36" s="20"/>
       <c r="F36" s="16"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="20"/>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -1917,31 +2200,31 @@
       <c r="E37" s="20"/>
       <c r="F37" s="16"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="23"/>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="79"/>
       <c r="F38" s="11"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="23"/>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
       <c r="F39" s="11"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="23"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
+      <c r="D40" s="79"/>
+      <c r="E40" s="79"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1949,7 +2232,7 @@
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="15"/>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -1957,7 +2240,7 @@
       <c r="E42" s="15"/>
       <c r="F42" s="15"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -1965,7 +2248,7 @@
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -1973,7 +2256,7 @@
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -1981,7 +2264,7 @@
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -1989,7 +2272,7 @@
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -1997,7 +2280,7 @@
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -2005,7 +2288,7 @@
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
@@ -2013,7 +2296,7 @@
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="9"/>
       <c r="C53" s="9"/>
@@ -2021,7 +2304,7 @@
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
@@ -2029,7 +2312,7 @@
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -2037,7 +2320,7 @@
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
@@ -2045,7 +2328,7 @@
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
@@ -2053,7 +2336,7 @@
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
@@ -2061,7 +2344,7 @@
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
@@ -2069,7 +2352,7 @@
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
@@ -2077,7 +2360,7 @@
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
@@ -2085,7 +2368,7 @@
       <c r="E61" s="7"/>
       <c r="F61" s="7"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
@@ -2093,7 +2376,7 @@
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
@@ -2101,7 +2384,7 @@
       <c r="E63" s="7"/>
       <c r="F63" s="7"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -2109,7 +2392,7 @@
       <c r="E64" s="7"/>
       <c r="F64" s="7"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
@@ -2117,7 +2400,7 @@
       <c r="E65" s="7"/>
       <c r="F65" s="7"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
@@ -2125,7 +2408,7 @@
       <c r="E66" s="7"/>
       <c r="F66" s="7"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
@@ -2133,7 +2416,7 @@
       <c r="E67" s="7"/>
       <c r="F67" s="7"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
@@ -2141,7 +2424,7 @@
       <c r="E68" s="7"/>
       <c r="F68" s="7"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
@@ -2149,7 +2432,7 @@
       <c r="E69" s="7"/>
       <c r="F69" s="7"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
@@ -2157,7 +2440,7 @@
       <c r="E70" s="7"/>
       <c r="F70" s="7"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
@@ -2165,7 +2448,7 @@
       <c r="E71" s="7"/>
       <c r="F71" s="7"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -2173,7 +2456,7 @@
       <c r="E72" s="7"/>
       <c r="F72" s="7"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -2199,13 +2482,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B148"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" style="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.453125" style="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="30" t="str">
         <f>INFO!B7</f>
         <v>BNII</v>
@@ -2215,723 +2498,767 @@
         <v>AU5800</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="43">
+        <v>29.8</v>
+      </c>
+      <c r="B2" s="44">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="41">
+        <v>31.1</v>
+      </c>
+      <c r="B3" s="42">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="43">
+        <v>62.7</v>
+      </c>
+      <c r="B4" s="44">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="41">
+        <v>72.2</v>
+      </c>
+      <c r="B5" s="42">
+        <v>64.900000000000006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="43">
+        <v>59.8</v>
+      </c>
+      <c r="B6" s="44">
+        <v>65.099999999999994</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="41">
+        <v>57.9</v>
+      </c>
+      <c r="B7" s="42">
+        <v>68.900000000000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="43">
+        <v>57</v>
+      </c>
+      <c r="B8" s="44">
+        <v>76.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="41">
+        <v>98.2</v>
+      </c>
+      <c r="B9" s="42">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="43">
+        <v>104</v>
+      </c>
+      <c r="B10" s="44">
+        <v>84.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="41">
+        <v>99.1</v>
+      </c>
+      <c r="B11" s="42">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="43">
+        <v>90.8</v>
+      </c>
+      <c r="B12" s="44">
+        <v>98.100000000000009</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="41">
+        <v>119</v>
+      </c>
+      <c r="B13" s="42">
+        <v>121.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="43">
         <v>116</v>
       </c>
-      <c r="B2" s="44">
+      <c r="B14" s="44">
         <v>123.5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="41">
-        <v>99.1</v>
-      </c>
-      <c r="B3" s="42">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="43">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="41">
+        <v>150</v>
+      </c>
+      <c r="B15" s="42">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="43">
+        <v>119</v>
+      </c>
+      <c r="B16" s="44">
+        <v>150.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="41">
+        <v>180</v>
+      </c>
+      <c r="B17" s="42">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="43">
+        <v>145</v>
+      </c>
+      <c r="B18" s="44">
+        <v>180.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="41">
+        <v>183</v>
+      </c>
+      <c r="B19" s="42">
+        <v>186.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="43">
         <v>156</v>
       </c>
-      <c r="B4" s="44">
+      <c r="B20" s="44">
         <v>188.9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="41">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="43">
         <v>241</v>
       </c>
-      <c r="B5" s="42">
+      <c r="B21" s="44">
         <v>240.6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="43">
-        <v>868</v>
-      </c>
-      <c r="B6" s="42">
-        <v>1238.9000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="43">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="41">
         <v>217</v>
       </c>
-      <c r="B7" s="42">
+      <c r="B22" s="42">
+        <v>240.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="43">
+        <v>217</v>
+      </c>
+      <c r="B23" s="44">
         <v>278.5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="41">
-        <v>104</v>
-      </c>
-      <c r="B8" s="44">
-        <v>84.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="43">
-        <v>29.8</v>
-      </c>
-      <c r="B9" s="42">
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="41">
-        <v>768</v>
-      </c>
-      <c r="B10" s="44">
-        <v>974.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="43">
-        <v>1290</v>
-      </c>
-      <c r="B11" s="42">
-        <v>1612</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="41">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="41">
+        <v>312</v>
+      </c>
+      <c r="B24" s="42">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="43">
+        <v>363</v>
+      </c>
+      <c r="B25" s="44">
+        <v>420.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="41">
+        <v>381</v>
+      </c>
+      <c r="B26" s="42">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="43">
+        <v>511</v>
+      </c>
+      <c r="B27" s="44">
+        <v>537.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="41">
+        <v>347</v>
+      </c>
+      <c r="B28" s="42">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="43">
+        <v>542</v>
+      </c>
+      <c r="B29" s="44">
+        <v>571.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="41">
+        <v>402</v>
+      </c>
+      <c r="B30" s="42">
+        <v>573.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="43">
         <v>465</v>
       </c>
-      <c r="B12" s="44">
+      <c r="B31" s="44">
         <v>632.6</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="43">
-        <v>470</v>
-      </c>
-      <c r="B13" s="42">
-        <v>815.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="41">
-        <v>1700</v>
-      </c>
-      <c r="B14" s="44">
-        <v>2182</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="43">
-        <v>31.1</v>
-      </c>
-      <c r="B15" s="42">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="43">
-        <v>72.2</v>
-      </c>
-      <c r="B16" s="42">
-        <v>64.900000000000006</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="41">
-        <v>119</v>
-      </c>
-      <c r="B17" s="44">
-        <v>121.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="43">
-        <v>415</v>
-      </c>
-      <c r="B18" s="42">
-        <v>782.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="41">
-        <v>145</v>
-      </c>
-      <c r="B19" s="44">
-        <v>180.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="43">
-        <v>183</v>
-      </c>
-      <c r="B20" s="42">
-        <v>186.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="41">
-        <v>363</v>
-      </c>
-      <c r="B21" s="44">
-        <v>420.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="43">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="41">
         <v>500</v>
       </c>
-      <c r="B22" s="42">
+      <c r="B32" s="42">
         <v>642.25</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="43">
-        <v>682</v>
-      </c>
-      <c r="B23" s="42">
-        <v>875.61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="46">
-        <v>881</v>
-      </c>
-      <c r="B24" s="46">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="46">
-        <v>634</v>
-      </c>
-      <c r="B25" s="46">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="46">
-        <v>312</v>
-      </c>
-      <c r="B26" s="46">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="41">
-        <v>1290</v>
-      </c>
-      <c r="B27" s="44">
-        <v>2080.88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="43">
-        <v>98.2</v>
-      </c>
-      <c r="B28" s="42">
-        <v>83.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="41">
-        <v>180</v>
-      </c>
-      <c r="B29" s="44">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="43">
-        <v>57.9</v>
-      </c>
-      <c r="B30" s="42">
-        <v>68.900000000000006</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="41">
-        <v>59.8</v>
-      </c>
-      <c r="B31" s="44">
-        <v>65.099999999999994</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="41">
-        <v>62.7</v>
-      </c>
-      <c r="B32" s="44">
-        <v>51.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="43">
-        <v>511</v>
-      </c>
-      <c r="B33" s="42">
-        <v>537.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="B33" s="44">
+        <v>666.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="41">
         <v>667</v>
       </c>
-      <c r="B34" s="44">
+      <c r="B34" s="42">
         <v>770.9</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="43"/>
-      <c r="B35" s="42"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="41"/>
-      <c r="B36" s="44"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="43"/>
-      <c r="B37" s="42"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="46"/>
-      <c r="B38" s="44"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="43"/>
-      <c r="B39" s="44"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="41"/>
-      <c r="B40" s="42"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="43"/>
-      <c r="B41" s="44"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="41"/>
-      <c r="B42" s="42"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="43"/>
-      <c r="B43" s="44"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="41"/>
-      <c r="B44" s="42"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="41"/>
-      <c r="B45" s="42"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="43"/>
-      <c r="B46" s="44"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="41"/>
-      <c r="B47" s="42"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="43">
+        <v>415</v>
+      </c>
+      <c r="B35" s="44">
+        <v>782.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="41">
+        <v>634</v>
+      </c>
+      <c r="B36" s="42">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="43">
+        <v>470</v>
+      </c>
+      <c r="B37" s="44">
+        <v>815.9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="41">
+        <v>682</v>
+      </c>
+      <c r="B38" s="42">
+        <v>875.61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="43">
+        <v>768</v>
+      </c>
+      <c r="B39" s="44">
+        <v>974.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="41">
+        <v>881</v>
+      </c>
+      <c r="B40" s="42">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="43">
+        <v>532</v>
+      </c>
+      <c r="B41" s="44">
+        <v>1041.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="41">
+        <v>919</v>
+      </c>
+      <c r="B42" s="42">
+        <v>1215.9000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="43">
+        <v>868</v>
+      </c>
+      <c r="B43" s="44">
+        <v>1238.9000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="41">
+        <v>1290</v>
+      </c>
+      <c r="B44" s="42">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="43">
+        <v>1290</v>
+      </c>
+      <c r="B45" s="44">
+        <v>2080.88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="41">
+        <v>1700</v>
+      </c>
+      <c r="B46" s="42">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="43"/>
       <c r="B48" s="44"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="41"/>
       <c r="B49" s="42"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="43"/>
       <c r="B50" s="44"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="41"/>
       <c r="B51" s="42"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="43"/>
       <c r="B52" s="44"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="41"/>
       <c r="B53" s="42"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="43"/>
       <c r="B54" s="44"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="41"/>
       <c r="B55" s="42"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="43"/>
       <c r="B56" s="44"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="41"/>
       <c r="B57" s="42"/>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="43"/>
       <c r="B58" s="44"/>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="41"/>
       <c r="B59" s="42"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="43"/>
       <c r="B60" s="44"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="41"/>
       <c r="B61" s="42"/>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="43"/>
       <c r="B62" s="44"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="41"/>
       <c r="B63" s="42"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="43"/>
       <c r="B64" s="44"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="41"/>
       <c r="B65" s="42"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="43"/>
       <c r="B66" s="44"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="41"/>
       <c r="B67" s="42"/>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="43"/>
       <c r="B68" s="44"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="41"/>
       <c r="B69" s="42"/>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="43"/>
       <c r="B70" s="44"/>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="41"/>
       <c r="B71" s="42"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="43"/>
       <c r="B72" s="44"/>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="41"/>
       <c r="B73" s="42"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="43"/>
       <c r="B74" s="44"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="41"/>
       <c r="B75" s="42"/>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="43"/>
       <c r="B76" s="44"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="41"/>
       <c r="B77" s="42"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="43"/>
       <c r="B78" s="44"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="41"/>
       <c r="B79" s="42"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="43"/>
       <c r="B80" s="44"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="41"/>
       <c r="B81" s="42"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="43"/>
       <c r="B82" s="44"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="41"/>
       <c r="B83" s="42"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="43"/>
       <c r="B84" s="44"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="41"/>
       <c r="B85" s="42"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="43"/>
       <c r="B86" s="44"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="41"/>
       <c r="B87" s="42"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="43"/>
       <c r="B88" s="44"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="41"/>
       <c r="B89" s="42"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="43"/>
       <c r="B90" s="44"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="41"/>
       <c r="B91" s="42"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="43"/>
       <c r="B92" s="44"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="41"/>
       <c r="B93" s="42"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="43"/>
       <c r="B94" s="44"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="41"/>
       <c r="B95" s="42"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="43"/>
       <c r="B96" s="44"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="41"/>
       <c r="B97" s="42"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="43"/>
       <c r="B98" s="44"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="41"/>
       <c r="B99" s="42"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="43"/>
       <c r="B100" s="44"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="41"/>
       <c r="B101" s="42"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="43"/>
       <c r="B102" s="44"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="41"/>
       <c r="B103" s="42"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="43"/>
       <c r="B104" s="44"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="41"/>
       <c r="B105" s="42"/>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="43"/>
       <c r="B106" s="44"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="41"/>
       <c r="B107" s="42"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="43"/>
       <c r="B108" s="44"/>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="41"/>
       <c r="B109" s="42"/>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="43"/>
       <c r="B110" s="44"/>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="41"/>
       <c r="B111" s="42"/>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="43"/>
       <c r="B112" s="44"/>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="41"/>
       <c r="B113" s="42"/>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="43"/>
       <c r="B114" s="44"/>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="41"/>
       <c r="B115" s="42"/>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" s="43"/>
       <c r="B116" s="44"/>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" s="41"/>
       <c r="B117" s="42"/>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="43"/>
       <c r="B118" s="44"/>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="41"/>
       <c r="B119" s="42"/>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="43"/>
       <c r="B120" s="44"/>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="41"/>
       <c r="B121" s="42"/>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="43"/>
       <c r="B122" s="44"/>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="41"/>
       <c r="B123" s="42"/>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" s="43"/>
       <c r="B124" s="44"/>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" s="41"/>
       <c r="B125" s="42"/>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" s="43"/>
       <c r="B126" s="44"/>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" s="41"/>
       <c r="B127" s="42"/>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" s="43"/>
       <c r="B128" s="44"/>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="41"/>
       <c r="B129" s="42"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="43"/>
       <c r="B130" s="44"/>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="41"/>
       <c r="B131" s="42"/>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="43"/>
       <c r="B132" s="44"/>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" s="41"/>
       <c r="B133" s="42"/>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" s="43"/>
       <c r="B134" s="44"/>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" s="41"/>
       <c r="B135" s="42"/>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" s="43"/>
       <c r="B136" s="44"/>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="41"/>
       <c r="B137" s="42"/>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="43"/>
       <c r="B138" s="44"/>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="41"/>
       <c r="B139" s="42"/>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="43"/>
       <c r="B140" s="44"/>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="41"/>
       <c r="B141" s="42"/>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="43"/>
       <c r="B142" s="44"/>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="41"/>
       <c r="B143" s="42"/>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="43"/>
       <c r="B144" s="44"/>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="41"/>
       <c r="B145" s="42"/>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="43"/>
       <c r="B146" s="44"/>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="41"/>
       <c r="B147" s="42"/>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="45"/>
       <c r="B148" s="33"/>
     </row>
@@ -2940,4 +3267,250 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="69"/>
+      <c r="B1" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="71" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="71" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="71" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="71" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="72" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="73">
+        <v>22.46</v>
+      </c>
+      <c r="C2" s="74">
+        <v>23.7</v>
+      </c>
+      <c r="D2" s="74">
+        <v>25.02</v>
+      </c>
+      <c r="E2" s="74">
+        <v>23.9</v>
+      </c>
+      <c r="F2" s="74">
+        <v>24.36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="73">
+        <v>23.31</v>
+      </c>
+      <c r="C3" s="74">
+        <v>22.3</v>
+      </c>
+      <c r="D3" s="74">
+        <v>24.25</v>
+      </c>
+      <c r="E3" s="74">
+        <v>24.68</v>
+      </c>
+      <c r="F3" s="75">
+        <v>24.09</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="72" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="73">
+        <v>21.05</v>
+      </c>
+      <c r="C4" s="74">
+        <v>26.6</v>
+      </c>
+      <c r="D4" s="74">
+        <v>23.33</v>
+      </c>
+      <c r="E4" s="74">
+        <v>23.2</v>
+      </c>
+      <c r="F4" s="75">
+        <v>26.64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="72" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="73">
+        <v>23.52</v>
+      </c>
+      <c r="C5" s="74">
+        <v>23.58</v>
+      </c>
+      <c r="D5" s="74">
+        <v>22.92</v>
+      </c>
+      <c r="E5" s="74">
+        <v>23.26</v>
+      </c>
+      <c r="F5" s="75">
+        <v>25.63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="72" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="76">
+        <v>22.21</v>
+      </c>
+      <c r="C6" s="77">
+        <v>24.73</v>
+      </c>
+      <c r="D6" s="77">
+        <v>23.95</v>
+      </c>
+      <c r="E6" s="77">
+        <v>22.83</v>
+      </c>
+      <c r="F6" s="78">
+        <v>22.12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="71" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="71" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="71" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="71" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="72" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="73">
+        <v>53.09</v>
+      </c>
+      <c r="C9" s="74">
+        <v>56.42</v>
+      </c>
+      <c r="D9" s="74">
+        <v>56.06</v>
+      </c>
+      <c r="E9" s="74">
+        <v>55.55</v>
+      </c>
+      <c r="F9" s="74">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="72" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="73">
+        <v>54.41</v>
+      </c>
+      <c r="C10" s="74">
+        <v>54.53</v>
+      </c>
+      <c r="D10" s="74">
+        <v>56.64</v>
+      </c>
+      <c r="E10" s="74">
+        <v>56.36</v>
+      </c>
+      <c r="F10" s="74">
+        <v>55.81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="72" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="73">
+        <v>54.35</v>
+      </c>
+      <c r="C11" s="74">
+        <v>56.62</v>
+      </c>
+      <c r="D11" s="74">
+        <v>54.16</v>
+      </c>
+      <c r="E11" s="74">
+        <v>55.33</v>
+      </c>
+      <c r="F11" s="74">
+        <v>55.45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="73">
+        <v>54.09</v>
+      </c>
+      <c r="C12" s="74">
+        <v>56.15</v>
+      </c>
+      <c r="D12" s="74">
+        <v>55.54</v>
+      </c>
+      <c r="E12" s="74">
+        <v>54.76</v>
+      </c>
+      <c r="F12" s="74">
+        <v>56.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="72" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="76">
+        <v>53.99</v>
+      </c>
+      <c r="C13" s="77">
+        <v>56.33</v>
+      </c>
+      <c r="D13" s="77">
+        <v>55.47</v>
+      </c>
+      <c r="E13" s="77">
+        <v>56.14</v>
+      </c>
+      <c r="F13" s="77">
+        <v>56.44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>